--- a/admin/public/templates/product-list-template.xlsx
+++ b/admin/public/templates/product-list-template.xlsx
@@ -561,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -653,10 +654,11 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Required. A full https:// product link.</t>
-        </is>
-      </c>
-    </row>
+          <t>Optional. A full https:// product link if you have one yet -- you can add it later, but the product cannot be published until it has one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
